--- a/inputs/portfolio_input_APL_h15_inflation.xlsx
+++ b/inputs/portfolio_input_APL_h15_inflation.xlsx
@@ -20,10 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -73,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -86,8 +83,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -540,7 +535,7 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>In de outputbestanden staat een extra tabblad "output". Daarin staan de doorgerekende portefeuillegewichten met direct daaronder de statistieken. De mean-variance frontier wordt in de notebook geplot en niet als tabel in Excel opgenomen.</t>
+          <t>In de outputbestanden staat een extra tabblad "output". Daarin staan de doorgerekende portefeuillegewichten met direct daaronder de statistieken. De frontier-punten staan in dezelfde tabel achter de portefeuilles. De frontier-plot wordt in de notebook gemaakt.</t>
         </is>
       </c>
     </row>
@@ -617,7 +612,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -636,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -661,7 +656,7 @@
           <t>Looninflatie NL</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -671,7 +666,7 @@
           <t>Prijsinflatie NL</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -681,7 +676,7 @@
           <t>Aandelen Opkomende Markten</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -691,7 +686,7 @@
           <t>Aandelen Wereld DC</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -701,7 +696,7 @@
           <t>Aandelen Wereld DC Unhedged</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -711,7 +706,7 @@
           <t>Bank Loans</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -721,7 +716,7 @@
           <t>Beursgenoteerd Vastgoed</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,177 +726,187 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Duitse Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
+          <t>Direct Lending Europa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMD HC</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
+          <t>Duitse Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMD LC</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
+          <t>EMD HC</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Euro IG Credits</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
+          <t>EMD LC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Euro ILBs</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
+          <t>Euro IG Credits</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Euro Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
+          <t>Euro ILBs</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global High Yield</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
+          <t>Euro Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global IG Credits</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
+          <t>Global High Yield</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global ILBs</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
+          <t>Global IG Credits</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grondstoffen</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
+          <t>Global ILBs</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
+          <t>Grondstoffen</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Internationaal Privaat Vastgoed</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italisaanse Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
+          <t>Internationaal Privaat Vastgoed</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nederlandse Hypotheken</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
+          <t>Italisaanse Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Privaat Infrastructuur</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
+          <t>Nederlandse Hypotheken</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Privaat Vastgoed NL</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
+          <t>Privaat Infrastructuur</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Privaat Vastgoed NL</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B27" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -916,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -977,13 +982,13 @@
           <t>Looninflatie NL</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -991,13 +996,13 @@
           <t>Prijsinflatie NL</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1005,19 +1010,19 @@
           <t>Aandelen Opkomende Markten</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1025,19 +1030,19 @@
           <t>Aandelen Wereld DC</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1045,19 +1050,19 @@
           <t>Aandelen Wereld DC Unhedged</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1065,13 +1070,13 @@
           <t>Bank Loans</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1079,19 +1084,19 @@
           <t>Beursgenoteerd Vastgoed</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1099,369 +1104,377 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Duitse Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+          <t>Direct Lending Europa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMD HC</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+          <t>Duitse Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMD LC</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6" t="n">
+          <t>EMD HC</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Euro IG Credits</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+          <t>EMD LC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Euro ILBs</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+          <t>Euro IG Credits</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Euro Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+          <t>Euro ILBs</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global High Yield</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+          <t>Euro Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global IG Credits</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+          <t>Global High Yield</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global ILBs</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+          <t>Global IG Credits</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grondstoffen</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
+          <t>Global ILBs</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+          <t>Grondstoffen</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Internationaal Privaat Vastgoed</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italisaanse Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
+          <t>Internationaal Privaat Vastgoed</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nederlandse Hypotheken</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+          <t>Italisaanse Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Privaat Infrastructuur</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
+          <t>Nederlandse Hypotheken</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Privaat Vastgoed NL</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
+          <t>Privaat Infrastructuur</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Privaat Vastgoed NL</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Group_Key</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Group_Name</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Group_1</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>VRW</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Group_2</t>
+          <t>Group_1</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
+          <t>VRW</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Group_3</t>
+          <t>Group_2</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Group_4</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
+          <t>Group_3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Group_4</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Group_5</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1474,7 +1487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1484,9 +1497,9 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1547,31 +1560,31 @@
           <t>Looninflatie NL</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="n">
+      <c r="B2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1581,31 +1594,31 @@
           <t>Prijsinflatie NL</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="n">
+      <c r="B3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1615,31 +1628,31 @@
           <t>Aandelen Opkomende Markten</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="5" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -1649,31 +1662,31 @@
           <t>Aandelen Wereld DC</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.3125</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="5" t="n">
         <v>0.3125</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1683,31 +1696,31 @@
           <t>Aandelen Wereld DC Unhedged</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.3125</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="5" t="n">
         <v>0.3125</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1717,31 +1730,31 @@
           <t>Bank Loans</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1751,31 +1764,31 @@
           <t>Beursgenoteerd Vastgoed</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1785,609 +1798,643 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Duitse Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6" t="n">
+          <t>Direct Lending Europa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMD HC</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.125</v>
+          <t>Duitse Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMD LC</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
+          <t>EMD HC</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
         <v>0.075</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0</v>
+      <c r="C12" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Euro IG Credits</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="n">
+          <t>EMD LC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Euro ILBs</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6" t="n">
+          <t>Euro IG Credits</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Euro Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="n">
+          <t>Euro ILBs</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global High Yield</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0.025</v>
+          <t>Euro Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global IG Credits</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0</v>
+          <t>Global High Yield</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global ILBs</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6" t="n">
+          <t>Global IG Credits</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grondstoffen</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.125</v>
+          <t>Global ILBs</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0</v>
+          <t>Grondstoffen</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Internationaal Privaat Vastgoed</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="n">
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italisaanse Staatsobligaties</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6" t="n">
+          <t>Internationaal Privaat Vastgoed</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nederlandse Hypotheken</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="n">
+          <t>Italisaanse Staatsobligaties</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Privaat Infrastructuur</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6" t="n">
+          <t>Nederlandse Hypotheken</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Privaat Vastgoed NL</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6" t="n">
+          <t>Privaat Infrastructuur</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Privaat Vastgoed NL</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6" t="n">
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="n">
         <v>0</v>
       </c>
     </row>
